--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484240_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484240_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>P. MARTINEZ ALEJANO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.689</v>
+        <v>5.6648</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0879</v>
+        <v>4.246</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6011</v>
+        <v>1.4188</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7111</v>
+        <v>0.6698</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4956</v>
+        <v>1.1136</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2156</v>
+        <v>-0.4437</v>
       </c>
       <c r="J2" t="n">
-        <v>3.335</v>
+        <v>2.7362</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2541</v>
+        <v>3.584</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0809</v>
+        <v>-0.8478</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6239</v>
+        <v>-2.0664</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7585</v>
+        <v>-2.4705</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1346</v>
+        <v>0.4041</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5627</v>
+        <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5556</v>
+        <v>1.0889</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0031</v>
+        <v>1.2761</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4475</v>
+        <v>-0.1872</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0549</v>
+        <v>3.7107</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.0549</v>
+        <v>2.3824</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1097</v>
+        <v>1.3283</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3268</v>
+        <v>4.7971</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9937</v>
+        <v>4.3594</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3331</v>
+        <v>0.4377</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8147</v>
+        <v>2.7111</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1525</v>
+        <v>2.4956</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3377</v>
+        <v>0.2156</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7836</v>
+        <v>3.335</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5812</v>
+        <v>3.2541</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2023</v>
+        <v>0.0809</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9688</v>
+        <v>-0.6239</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4287</v>
+        <v>-0.7585</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5401</v>
+        <v>0.1346</v>
       </c>
       <c r="P3" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R3" t="n">
         <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5939</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9096</v>
+        <v>1.2746</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6843</v>
+        <v>-0.6109</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3321</v>
+        <v>0.0549</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2772</v>
+        <v>-0.0549</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0549</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. MARTINEZ ALEJANO</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4703</v>
+        <v>3.7109</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2149</v>
+        <v>2.8408</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2554</v>
+        <v>0.8701</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6698</v>
+        <v>1.8147</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1136</v>
+        <v>2.1525</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4437</v>
+        <v>-0.3377</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7362</v>
+        <v>2.7836</v>
       </c>
       <c r="K4" t="n">
-        <v>3.584</v>
+        <v>2.5812</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8478</v>
+        <v>0.2023</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0664</v>
+        <v>-0.9688</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.4705</v>
+        <v>-0.4287</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4041</v>
+        <v>-0.5401</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3441</v>
+        <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1056</v>
+        <v>0.9781</v>
       </c>
       <c r="T4" t="n">
-        <v>0.245</v>
+        <v>0.7567</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3506</v>
+        <v>0.2213</v>
       </c>
       <c r="V4" t="n">
-        <v>3.7107</v>
+        <v>0.3321</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3824</v>
+        <v>0.2772</v>
       </c>
       <c r="X4" t="n">
-        <v>1.3283</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.489</v>
+        <v>1.7812</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6615</v>
+        <v>1.6814</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1725</v>
+        <v>0.0999</v>
       </c>
       <c r="G5" t="n">
         <v>2.094</v>
@@ -844,13 +844,13 @@
         <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2229</v>
+        <v>0.5152</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1942</v>
+        <v>1.2141</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-0.6989</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2186</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4664</v>
+        <v>0.3412</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1879</v>
+        <v>1.0773</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6543</v>
+        <v>-0.736</v>
       </c>
       <c r="G6" t="n">
         <v>-2.6773</v>
@@ -922,13 +922,13 @@
         <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5938</v>
+        <v>0.2139</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3961</v>
+        <v>0.4933</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1976</v>
+        <v>-0.2793</v>
       </c>
       <c r="V6" t="n">
         <v>1.8279</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4818</v>
+        <v>-0.4372</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5753</v>
+        <v>1.8499</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.0571</v>
+        <v>-2.2872</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2641</v>
+        <v>-1.2674</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4165</v>
+        <v>-1.2003</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8476</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>4.9402</v>
+        <v>1.7336</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4175</v>
+        <v>0.4515</v>
       </c>
       <c r="L7" t="n">
-        <v>2.5227</v>
+        <v>1.2821</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.6761</v>
+        <v>-3.001</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.001</v>
+        <v>-1.6518</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6751</v>
+        <v>-1.3492</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.7348</v>
+        <v>0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.0789</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3441</v>
+        <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9265</v>
+        <v>0.2442</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9372</v>
+        <v>0.1164</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0106</v>
+        <v>0.1278</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.9376</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7768</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3357</v>
+        <v>-1.0492</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1421</v>
+        <v>2.0896</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4778</v>
+        <v>-3.1388</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2674</v>
+        <v>2.2641</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2003</v>
+        <v>0.4165</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06710000000000001</v>
+        <v>1.8476</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7336</v>
+        <v>4.9402</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4515</v>
+        <v>2.4175</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2821</v>
+        <v>2.5227</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.001</v>
+        <v>-2.6761</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6518</v>
+        <v>-2.001</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3492</v>
+        <v>-0.6751</v>
       </c>
       <c r="P8" t="n">
-        <v>0.586</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-5.0789</v>
       </c>
       <c r="R8" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6543</v>
+        <v>1.3592</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5915</v>
+        <v>1.4515</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.0924</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.9376</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.7768</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6505</v>
+        <v>-2.2196</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6122</v>
+        <v>-0.9362</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0382</v>
+        <v>-1.2834</v>
       </c>
       <c r="G9" t="n">
         <v>-6.8393</v>
@@ -1156,13 +1156,13 @@
         <v>2.1488</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3293</v>
+        <v>1.7602</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1463</v>
+        <v>1.8223</v>
       </c>
       <c r="U9" t="n">
-        <v>0.183</v>
+        <v>-0.0621</v>
       </c>
       <c r="V9" t="n">
         <v>1.8828</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4676</v>
+        <v>-2.3798</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3272</v>
+        <v>-1.539</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1404</v>
+        <v>-0.8408</v>
       </c>
       <c r="G10" t="n">
         <v>-3.439</v>
@@ -1234,13 +1234,13 @@
         <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0053</v>
+        <v>0.0825</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4566</v>
+        <v>0.3316</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5487</v>
+        <v>-0.2491</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.526</v>
+        <v>-2.9521</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9788</v>
+        <v>-1.5138</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5472</v>
+        <v>-1.4383</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3976</v>
@@ -1312,13 +1312,13 @@
         <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5739</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4237</v>
+        <v>0.0413</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1503</v>
+        <v>-0.0413</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1638</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.0471</v>
+        <v>7.257300000000003</v>
       </c>
       <c r="E12" t="n">
-        <v>12.9451</v>
+        <v>14.1554</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.8979</v>
+        <v>-6.898</v>
       </c>
       <c r="G12" t="n">
         <v>-6.0669</v>
@@ -1390,10 +1390,10 @@
         <v>14.6505</v>
       </c>
       <c r="S12" t="n">
-        <v>5.6953</v>
+        <v>6.905999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>7.567500000000001</v>
+        <v>8.777899999999999</v>
       </c>
       <c r="U12" t="n">
         <v>-1.8721</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9159</v>
+        <v>1.8471</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6742</v>
+        <v>2.117</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7583</v>
+        <v>-0.2699</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3751</v>
+        <v>0.5967</v>
       </c>
       <c r="H13" t="n">
-        <v>0.243</v>
+        <v>-0.2118</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1321</v>
+        <v>0.8085</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4884</v>
+        <v>2.1843</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7601</v>
+        <v>1.375</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7284</v>
+        <v>0.8093</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1133</v>
+        <v>-1.5876</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.517</v>
+        <v>-1.5868</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4037</v>
+        <v>-0.0008</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7814</v>
+        <v>1.9534</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5491</v>
+        <v>-0.6128</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1474</v>
+        <v>0.0229</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.6357</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1638</v>
+        <v>0.8865</v>
       </c>
       <c r="W13" t="n">
-        <v>2.9917</v>
+        <v>0.8865</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7875</v>
+        <v>1.536</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2181</v>
+        <v>4.2697</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4306</v>
+        <v>-2.7337</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5967</v>
+        <v>1.3751</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2118</v>
+        <v>0.243</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8085</v>
+        <v>1.1321</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1843</v>
+        <v>2.4884</v>
       </c>
       <c r="K14" t="n">
-        <v>1.375</v>
+        <v>1.7601</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8093</v>
+        <v>0.7284</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5876</v>
+        <v>-1.1133</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5868</v>
+        <v>-1.517</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0008</v>
+        <v>0.4037</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6724</v>
+        <v>0.1691</v>
       </c>
       <c r="T14" t="n">
-        <v>0.124</v>
+        <v>0.743</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7964</v>
+        <v>-0.5738</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8865</v>
+        <v>1.1638</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8865</v>
+        <v>2.9917</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2534</v>
+        <v>0.4493</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1869</v>
+        <v>0.2175</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0665</v>
+        <v>0.2317</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1222</v>
@@ -1624,13 +1624,13 @@
         <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0726</v>
+        <v>0.6301</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2008</v>
+        <v>0.2037</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1281</v>
+        <v>0.4264</v>
       </c>
       <c r="V15" t="n">
         <v>0.9414</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3191</v>
+        <v>0.0789</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8219</v>
+        <v>0.923</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.141</v>
+        <v>-0.8441</v>
       </c>
       <c r="G16" t="n">
         <v>1.0399</v>
@@ -1702,13 +1702,13 @@
         <v>0.1953</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9999</v>
+        <v>-0.6019</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1678</v>
+        <v>-0.0667</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8321</v>
+        <v>-0.5352</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5545</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6538</v>
+        <v>-0.007</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3781</v>
+        <v>0.7826</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.032</v>
+        <v>-0.7895</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1527</v>
@@ -1780,13 +1780,13 @@
         <v>0.1953</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9151</v>
+        <v>-0.2683</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2421</v>
+        <v>0.1624</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6731</v>
+        <v>-0.4307</v>
       </c>
       <c r="V17" t="n">
         <v>1.2186</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7409</v>
+        <v>-0.5437</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7603</v>
+        <v>-0.5058</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5012</v>
+        <v>-0.0379</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0746</v>
+        <v>0.3947</v>
       </c>
       <c r="H18" t="n">
-        <v>1.954</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1206</v>
+        <v>0.485</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2577</v>
+        <v>0.4097</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8104</v>
+        <v>0.3287</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5527</v>
+        <v>0.0809</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1832</v>
+        <v>-0.015</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8565</v>
+        <v>-0.419</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6733</v>
+        <v>0.4041</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.4891</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.0613</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.5503</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="W18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-1.9534</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.9534</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-0.9327</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.7843</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-1.717</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-1.8828</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-1.3283</v>
-      </c>
       <c r="X18" t="n">
-        <v>-0.5545</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2801</v>
+        <v>-0.6047</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8092</v>
+        <v>0.3558</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4709</v>
+        <v>-0.9605</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3947</v>
+        <v>2.0746</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.09030000000000001</v>
+        <v>1.954</v>
       </c>
       <c r="I19" t="n">
-        <v>0.485</v>
+        <v>0.1206</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4097</v>
+        <v>3.2577</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3287</v>
+        <v>3.8104</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0809</v>
+        <v>-0.5527</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.015</v>
+        <v>-1.1832</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.419</v>
+        <v>-1.8565</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4041</v>
+        <v>0.6733</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2255</v>
+        <v>-0.7965</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2421</v>
+        <v>0.3798</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-1.1763</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3321</v>
+        <v>-1.8828</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-1.3283</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3321</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5205</v>
+        <v>-1.1474</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0645</v>
+        <v>1.6554</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5439</v>
+        <v>-2.8028</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7487</v>
+        <v>0.1309</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8572</v>
+        <v>-1.1509</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1086</v>
+        <v>1.2819</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7223</v>
+        <v>1.7234</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5605</v>
+        <v>0.5756</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1619</v>
+        <v>1.1478</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9737</v>
+        <v>-1.5925</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7032</v>
+        <v>-1.7265</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2704</v>
+        <v>0.134</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7037</v>
+        <v>-0.4271</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4679</v>
+        <v>0.2994</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2358</v>
+        <v>-0.7265</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.6056</v>
+        <v>-1.8279</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.3246</v>
+        <v>0.6093</v>
       </c>
       <c r="X20" t="n">
-        <v>0.719</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8994</v>
+        <v>-2.4011</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5543</v>
+        <v>0.855</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4537</v>
+        <v>-3.2562</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1309</v>
+        <v>1.9812</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1509</v>
+        <v>-0.3528</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2819</v>
+        <v>2.334</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7234</v>
+        <v>4.1784</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5756</v>
+        <v>1.1691</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1478</v>
+        <v>3.0093</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5925</v>
+        <v>-2.1971</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7265</v>
+        <v>-1.5219</v>
       </c>
       <c r="O21" t="n">
-        <v>0.134</v>
+        <v>-0.6753</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R21" t="n">
         <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1792</v>
+        <v>-0.2689</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1983</v>
+        <v>0.3063</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.3774</v>
+        <v>-0.5752</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8279</v>
+        <v>-2.16</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
         <v>-2.4373</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0831</v>
+        <v>-2.5579</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5517</v>
+        <v>-3.7723</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.6347</v>
+        <v>1.2144</v>
       </c>
       <c r="G22" t="n">
-        <v>1.9812</v>
+        <v>0.7487</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3528</v>
+        <v>0.8572</v>
       </c>
       <c r="I22" t="n">
-        <v>2.334</v>
+        <v>-0.1086</v>
       </c>
       <c r="J22" t="n">
-        <v>4.1784</v>
+        <v>1.7223</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1691</v>
+        <v>1.5605</v>
       </c>
       <c r="L22" t="n">
-        <v>3.0093</v>
+        <v>0.1619</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1971</v>
+        <v>-0.9737</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5219</v>
+        <v>-0.7032</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6753</v>
+        <v>-0.2704</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9534</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9508</v>
+        <v>-0.3336</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0029</v>
+        <v>-0.2399</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9538</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.16</v>
+        <v>-1.6056</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>-2.3246</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4373</v>
+        <v>0.719</v>
       </c>
     </row>
     <row r="23">
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0469</v>
+        <v>-3.3505</v>
       </c>
       <c r="E23" t="n">
-        <v>6.898</v>
+        <v>6.897900000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>-12.945</v>
+        <v>-10.2485</v>
       </c>
       <c r="G23" t="n">
         <v>6.0669</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6739999999999997</v>
+        <v>0.6739999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>5.3928</v>
@@ -2236,7 +2236,7 @@
         <v>-10.7277</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6672000000000002</v>
+        <v>0.6672</v>
       </c>
       <c r="P23" t="n">
         <v>-2.9303</v>
@@ -2248,22 +2248,22 @@
         <v>11.7203</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.6954</v>
+        <v>-2.999</v>
       </c>
       <c r="T23" t="n">
-        <v>1.872</v>
+        <v>1.8722</v>
       </c>
       <c r="U23" t="n">
-        <v>-7.567600000000001</v>
+        <v>-4.871</v>
       </c>
       <c r="V23" t="n">
         <v>-3.4884</v>
       </c>
       <c r="W23" t="n">
-        <v>3.549</v>
+        <v>3.548999999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-7.037600000000001</v>
+        <v>-7.0376</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484240_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484240_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>1.3283</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.1097</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3412</v>
+        <v>0.607</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0773</v>
+        <v>0.607</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.736</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.6773</v>
+        <v>0.607</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9788</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6986</v>
+        <v>0.607</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.244</v>
+        <v>0.607</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4899</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.754</v>
+        <v>0.607</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4334</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4889</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9445</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2139</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4933</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2793</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4372</v>
+        <v>-0.2658</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8499</v>
+        <v>0.4703</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2872</v>
+        <v>-0.736</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2674</v>
+        <v>-3.2843</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2003</v>
+        <v>-0.9788</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-2.3056</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7336</v>
+        <v>-1.8509</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4515</v>
+        <v>-0.4899</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2821</v>
+        <v>-1.361</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.001</v>
+        <v>-1.4334</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6518</v>
+        <v>-0.4889</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3492</v>
+        <v>-0.9445</v>
       </c>
       <c r="P7" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2442</v>
+        <v>0.2139</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1164</v>
+        <v>0.4933</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1278</v>
+        <v>-0.2793</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0492</v>
+        <v>-0.4372</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0896</v>
+        <v>1.8499</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1388</v>
+        <v>-2.2872</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2641</v>
+        <v>-1.2674</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4165</v>
+        <v>-1.2003</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8476</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>4.9402</v>
+        <v>1.7336</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4175</v>
+        <v>0.4515</v>
       </c>
       <c r="L8" t="n">
-        <v>2.5227</v>
+        <v>1.2821</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6761</v>
+        <v>-3.001</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.001</v>
+        <v>-1.6518</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6751</v>
+        <v>-1.3492</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.7348</v>
+        <v>0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.0789</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3441</v>
+        <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3592</v>
+        <v>0.2442</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4515</v>
+        <v>0.1164</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0924</v>
+        <v>0.1278</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.9376</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7768</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2196</v>
+        <v>-1.0492</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9362</v>
+        <v>2.0896</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2834</v>
+        <v>-3.1388</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.8393</v>
+        <v>2.2641</v>
       </c>
       <c r="H9" t="n">
-        <v>-6.4342</v>
+        <v>0.4165</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4051</v>
+        <v>1.8476</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.4144</v>
+        <v>4.9402</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.5496</v>
+        <v>2.4175</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1352</v>
+        <v>2.5227</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.4249</v>
+        <v>-2.6761</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.8846</v>
+        <v>-2.001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5403</v>
+        <v>-0.6751</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9767</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1721</v>
+        <v>-5.0789</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1488</v>
+        <v>2.3441</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7602</v>
+        <v>1.3592</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8223</v>
+        <v>1.4515</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0621</v>
+        <v>-0.0924</v>
       </c>
       <c r="V9" t="n">
-        <v>1.8828</v>
+        <v>-1.9376</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8279</v>
+        <v>0.7768</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0549</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3798</v>
+        <v>-2.2196</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.539</v>
+        <v>-0.9362</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8408</v>
+        <v>-1.2834</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.439</v>
+        <v>-6.8393</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.23</v>
+        <v>-6.4342</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.209</v>
+        <v>-0.4051</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8706</v>
+        <v>-3.4144</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1241</v>
+        <v>-3.5496</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9947</v>
+        <v>0.1352</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5684</v>
+        <v>-3.4249</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.354</v>
+        <v>-2.8846</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2144</v>
+        <v>-0.5403</v>
       </c>
       <c r="P10" t="n">
         <v>0.9767</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0825</v>
+        <v>1.7602</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3316</v>
+        <v>1.8223</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2491</v>
+        <v>-0.0621</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.8828</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CANAL FERRER</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9521</v>
+        <v>-2.3798</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5138</v>
+        <v>-1.539</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4383</v>
+        <v>-0.8408</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3976</v>
+        <v>-3.439</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7368</v>
+        <v>-0.23</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6609</v>
+        <v>-3.209</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5784</v>
+        <v>-1.8706</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.1241</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0138</v>
+        <v>-1.9947</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8192</v>
+        <v>-1.5684</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1445</v>
+        <v>-0.354</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6747</v>
+        <v>-1.2144</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.0825</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0413</v>
+        <v>0.3316</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0413</v>
+        <v>-0.2491</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. CANAL FERRER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,926 +1400,1310 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.257300000000003</v>
+        <v>-2.9521</v>
       </c>
       <c r="E12" t="n">
-        <v>14.1554</v>
+        <v>-1.5138</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.898</v>
+        <v>-1.4383</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.0669</v>
+        <v>-1.3976</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6741</v>
+        <v>-0.7368</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.3927</v>
+        <v>-0.6609</v>
       </c>
       <c r="J12" t="n">
-        <v>10.0605</v>
+        <v>-0.5784</v>
       </c>
       <c r="K12" t="n">
-        <v>10.7278</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6672</v>
+        <v>0.0138</v>
       </c>
       <c r="M12" t="n">
-        <v>-16.1274</v>
+        <v>-0.8192</v>
       </c>
       <c r="N12" t="n">
-        <v>-11.4017</v>
+        <v>-0.1445</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.7257</v>
+        <v>-0.6747</v>
       </c>
       <c r="P12" t="n">
-        <v>2.93</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.7206</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>14.6505</v>
+        <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>6.905999999999999</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>8.777899999999999</v>
+        <v>0.0413</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.8721</v>
+        <v>-0.0413</v>
       </c>
       <c r="V12" t="n">
-        <v>3.4884</v>
+        <v>-1.1638</v>
       </c>
       <c r="W12" t="n">
-        <v>7.037300000000001</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.5491</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8471</v>
+        <v>7.257300000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>2.117</v>
+        <v>14.1554</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2699</v>
+        <v>-6.898</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5967</v>
+        <v>-6.0669</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2118</v>
+        <v>-0.6741</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8085</v>
+        <v>-5.3927</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1843</v>
+        <v>10.0606</v>
       </c>
       <c r="K13" t="n">
-        <v>1.375</v>
+        <v>10.7278</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8093</v>
+        <v>-0.6671999999999998</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5876</v>
+        <v>-16.1274</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5868</v>
+        <v>-11.4017</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0008</v>
+        <v>-4.7257</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9767</v>
+        <v>2.93</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-11.7206</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9534</v>
+        <v>14.6505</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6128</v>
+        <v>6.906</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0229</v>
+        <v>8.777899999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6357</v>
+        <v>-1.8721</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8865</v>
+        <v>3.4884</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8865</v>
+        <v>7.0373</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
-      </c>
+        <v>-3.5491</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.536</v>
+        <v>1.8279</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2697</v>
+        <v>1.8279</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.7337</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3751</v>
+        <v>1.8279</v>
       </c>
       <c r="H14" t="n">
-        <v>0.243</v>
+        <v>0.614</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1321</v>
+        <v>1.214</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4884</v>
+        <v>1.8279</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7601</v>
+        <v>0.614</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7284</v>
+        <v>1.214</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1133</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.517</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4037</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1691</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.743</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5738</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.9917</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4493</v>
+        <v>1.536</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2175</v>
+        <v>4.2697</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2317</v>
+        <v>-2.7337</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1222</v>
+        <v>1.3751</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7094</v>
+        <v>0.243</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.8316</v>
+        <v>1.1321</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2281</v>
+        <v>2.4884</v>
       </c>
       <c r="K15" t="n">
-        <v>1.659</v>
+        <v>1.7601</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.8871</v>
+        <v>0.7284</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8941</v>
+        <v>-1.1133</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0504</v>
+        <v>-1.517</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9445</v>
+        <v>0.4037</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6301</v>
+        <v>0.1691</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2037</v>
+        <v>0.743</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4264</v>
+        <v>-0.5738</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9414</v>
+        <v>1.1638</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>2.9917</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0789</v>
+        <v>1.2279</v>
       </c>
       <c r="E16" t="n">
-        <v>0.923</v>
+        <v>1.2279</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8441</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0399</v>
+        <v>1.2279</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8885</v>
+        <v>1.2279</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9283</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9897</v>
+        <v>1.2279</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2648</v>
+        <v>1.2279</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2544</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0502</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6237</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6739000000000001</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6019</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0667</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5352</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.007</v>
+        <v>1.221</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7826</v>
+        <v>1.221</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7895</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1527</v>
+        <v>1.221</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3953</v>
+        <v>0.614</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2426</v>
+        <v>0.607</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5984</v>
+        <v>1.221</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5718</v>
+        <v>0.614</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0266</v>
+        <v>0.607</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5542</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8235</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2692</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2683</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1624</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4307</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>A. RECIO PINOL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5437</v>
+        <v>0.6262</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5058</v>
+        <v>0.8961</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0379</v>
+        <v>-0.2699</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3947</v>
+        <v>-0.6243</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.8258</v>
       </c>
       <c r="I18" t="n">
-        <v>0.485</v>
+        <v>0.2015</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4097</v>
+        <v>0.9634</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3287</v>
+        <v>0.761</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0809</v>
+        <v>0.2023</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.015</v>
+        <v>-1.5876</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.419</v>
+        <v>-1.5868</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4041</v>
+        <v>-0.0008</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4891</v>
+        <v>-0.6128</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0613</v>
+        <v>0.0229</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5503</v>
+        <v>-0.6357</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3321</v>
+        <v>0.8865</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6047</v>
+        <v>0.4493</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3558</v>
+        <v>0.2175</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9605</v>
+        <v>0.2317</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0746</v>
+        <v>-1.1222</v>
       </c>
       <c r="H19" t="n">
-        <v>1.954</v>
+        <v>1.7094</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1206</v>
+        <v>-2.8316</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2577</v>
+        <v>-0.2281</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8104</v>
+        <v>1.659</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5527</v>
+        <v>-1.8871</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1832</v>
+        <v>-0.8941</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8565</v>
+        <v>0.0504</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6733</v>
+        <v>-0.9445</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7965</v>
+        <v>0.6301</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3798</v>
+        <v>0.2037</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1763</v>
+        <v>0.4264</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8828</v>
+        <v>0.9414</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.3283</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1474</v>
+        <v>0.0789</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6554</v>
+        <v>0.923</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8028</v>
+        <v>-0.8441</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1309</v>
+        <v>1.0399</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1509</v>
+        <v>-0.8885</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2819</v>
+        <v>1.9283</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7234</v>
+        <v>0.9897</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5756</v>
+        <v>-0.2648</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1478</v>
+        <v>1.2544</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5925</v>
+        <v>0.0502</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7265</v>
+        <v>-0.6237</v>
       </c>
       <c r="O20" t="n">
-        <v>0.134</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4271</v>
+        <v>-0.6019</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2994</v>
+        <v>-0.0667</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7265</v>
+        <v>-0.5352</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8279</v>
+        <v>-0.5545</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4373</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4011</v>
+        <v>-0.007</v>
       </c>
       <c r="E21" t="n">
-        <v>0.855</v>
+        <v>0.7826</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.2562</v>
+        <v>-0.7895</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9812</v>
+        <v>-1.1527</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3528</v>
+        <v>-1.3953</v>
       </c>
       <c r="I21" t="n">
-        <v>2.334</v>
+        <v>0.2426</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1784</v>
+        <v>-0.5984</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1691</v>
+        <v>-0.5718</v>
       </c>
       <c r="L21" t="n">
-        <v>3.0093</v>
+        <v>-0.0266</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1971</v>
+        <v>-0.5542</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5219</v>
+        <v>-0.8235</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6753</v>
+        <v>0.2692</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2689</v>
+        <v>-0.2683</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3063</v>
+        <v>0.1624</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5752</v>
+        <v>-0.4307</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.16</v>
+        <v>1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5579</v>
+        <v>-0.5437</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7723</v>
+        <v>-0.5058</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2144</v>
+        <v>-0.0379</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7487</v>
+        <v>0.3947</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8572</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1086</v>
+        <v>0.485</v>
       </c>
       <c r="J22" t="n">
-        <v>1.7223</v>
+        <v>0.4097</v>
       </c>
       <c r="K22" t="n">
-        <v>1.5605</v>
+        <v>0.3287</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1619</v>
+        <v>0.0809</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9737</v>
+        <v>-0.015</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7032</v>
+        <v>-0.419</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2704</v>
+        <v>0.4041</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3674</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3336</v>
+        <v>-0.4891</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2399</v>
+        <v>0.0613</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.5503</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6056</v>
+        <v>0.3321</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.3246</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.719</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3505</v>
+        <v>-1.1474</v>
       </c>
       <c r="E23" t="n">
-        <v>6.897900000000002</v>
+        <v>1.6554</v>
       </c>
       <c r="F23" t="n">
+        <v>-2.8028</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.1509</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.2819</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.7234</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.5756</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.1478</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.5925</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.7265</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.4271</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.7265</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A. ABELLO GIRVES</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-1.8327</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.8721</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.9605</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.8466</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1206</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.0298</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.5825</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.5527</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.1832</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.8565</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.6733</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.7965</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-1.1763</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.8828</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-1.3283</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>F. VILAR FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-2.5579</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.7723</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.2144</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.7487</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.8572</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.1086</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.7223</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.5605</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.9737</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.7032</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.2704</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.3336</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.2399</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.09370000000000001</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.6056</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-2.3246</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>P. CARRION SORIANO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-4.2291</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.9729</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-3.2562</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1533</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.9667</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.3504</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.5551</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.7953</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.1971</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.5219</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.6753</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.2689</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.5752</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484240_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-3.3506</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6.898000000000001</v>
+      </c>
+      <c r="F27" t="n">
         <v>-10.2485</v>
       </c>
-      <c r="G23" t="n">
-        <v>6.0669</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.6739999999999999</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="G27" t="n">
+        <v>6.0668</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="I27" t="n">
         <v>5.3928</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J27" t="n">
         <v>16.1274</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K27" t="n">
         <v>11.4018</v>
       </c>
-      <c r="L23" t="n">
-        <v>4.7256</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="L27" t="n">
+        <v>4.725600000000001</v>
+      </c>
+      <c r="M27" t="n">
         <v>-10.0605</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N27" t="n">
         <v>-10.7277</v>
       </c>
-      <c r="O23" t="n">
-        <v>0.6672</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="O27" t="n">
+        <v>0.6672000000000002</v>
+      </c>
+      <c r="P27" t="n">
         <v>-2.9303</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q27" t="n">
         <v>-14.6506</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R27" t="n">
         <v>11.7203</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S27" t="n">
         <v>-2.999</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T27" t="n">
         <v>1.8722</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U27" t="n">
         <v>-4.871</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V27" t="n">
         <v>-3.4884</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W27" t="n">
         <v>3.548999999999999</v>
       </c>
-      <c r="X23" t="n">
-        <v>-7.0376</v>
-      </c>
+      <c r="X27" t="n">
+        <v>-7.037599999999999</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
